--- a/Black Body Irradiance Sensor Breakout/Irrad Breakout Board bom (1).xlsx
+++ b/Black Body Irradiance Sensor Breakout/Irrad Breakout Board bom (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/E70C4B3F8F5DC8BF/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kellh\Documents\LHR\Power-Generation-Blackbody\Black Body Irradiance Sensor Breakout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8163D2A3-BF7F-4DF5-A322-F9ED0115F0B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85380680-BBAF-4691-8025-32459DEC50B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="158" yWindow="8" windowWidth="13072" windowHeight="12622" xr2:uid="{9CAF1304-F0CE-43A0-BAAF-B0C2CCDCCB33}"/>
+    <workbookView xWindow="0" yWindow="638" windowWidth="21668" windowHeight="12352" xr2:uid="{9CAF1304-F0CE-43A0-BAAF-B0C2CCDCCB33}"/>
   </bookViews>
   <sheets>
     <sheet name="bom" sheetId="1" r:id="rId1"/>
@@ -399,7 +399,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -577,6 +577,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -740,9 +752,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1153,10 +1168,10 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1186,10 +1201,10 @@
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
